--- a/analytics/appraiser-scorecard/Appraiser_Performance.xlsx
+++ b/analytics/appraiser-scorecard/Appraiser_Performance.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Deal Detail" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="By Appraiser" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="By Appraiser x Carrier" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="By Appraiser x Claim Type" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026 Like-for-Like" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="By Appraiser" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="By Appraiser x Carrier" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="By Appraiser x Claim Type" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Deal Detail'!$A$1:$L$584</definedName>
@@ -79,7 +80,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +100,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -128,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -155,6 +161,10 @@
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -28600,6 +28610,257 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>2026 only — the like-for-like comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Assignment is by capacity with no set rule, so caseloads are close to randomly assigned. A balance check confirmed this on carrier, roof size, claim type and state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>But TIME was not balanced: Mitchell and Jakub only appear in 2026, while Zack and Jason span 2025-2026, and 2026 ran about 8% higher. This tab removes that distortion by using 2026 deals only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>This is the most defensible ranking in the workbook. It supersedes the all-years table on the 'By Appraiser' tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Appraiser</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Deals</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Adjusted vs expected</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>90% low</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>90% high</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Median $</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Own-data weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>ZACK</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>136</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>0.1672116248981203</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0.3492632621434042</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>18348.68</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>0.8433290381159456</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>MITCHELL</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>0.07958200858013439</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.08323731325129639</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.2937775911054332</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>18801.36</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>0.7529410403847215</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>JASON</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>-0.1174903694072523</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>-0.2499023718610697</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>0.0121530966318723</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>16034.56</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>0.7983034870471593</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>JAKUB</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>-0.2162149540607532</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>-0.4687552210724135</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>-0.0002978463507272</v>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>13951.115</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>0.6006419583794168</v>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>ROBUSTNESS: the model was re-run with 10 different bootstrap seeds. Jakub's interval excluded zero in 8 of 10; nobody else's did in any of the 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Jakub's upper bound sits within 0.4 percentage points of zero in every run, so this is a BORDERLINE result, not an established one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Zack's lower bound lands at +0.0% in all 10 seeds - the strongest positive signal, but it never clears zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Bottom line: Zack is the strongest performer on like-for-like data; Jakub is the weakest and is the only near-significant finding; Mitchell and Jason are indistinguishable from average.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Mitchell topped the all-years table at +14%. On 2026-only data that falls to +8%, so part of his earlier lead was the stronger 2026 book, not the appraiser.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -28945,7 +29206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29239,7 +29500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
